--- a/AAII_Financials/Yearly/UAL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/UAL_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
   <si>
     <t>UAL</t>
   </si>
@@ -656,196 +656,209 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>53717000</v>
+      </c>
+      <c r="E8" s="3">
         <v>44955000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>24634000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>15355000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>43259000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>41303000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>37784000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>36558000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>37864000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>38901000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>38279000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>37152000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>37110000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>21060000</v>
+      </c>
+      <c r="E9" s="3">
         <v>20393000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>11862000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8375000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>16427000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>16605000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>13968000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12604000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>14420000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>18955000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>19611000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>20290000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>20894000</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>32657000</v>
+      </c>
+      <c r="E10" s="3">
         <v>24562000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12772000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6980000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>26832000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>24698000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>23816000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>23954000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>23444000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>19946000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>18668000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>16862000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>16216000</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -862,8 +875,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -903,9 +917,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,93 +962,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>814000</v>
+      </c>
+      <c r="E14" s="3">
         <v>140000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-3367000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-2643000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>187000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>482000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>141000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>694000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>227000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>410000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>470000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1369000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>579000</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2671000</v>
+      </c>
+      <c r="E15" s="3">
         <v>2456000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2485000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2488000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2288000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2165000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2096000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1977000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1819000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1679000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1689000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1522000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1547000</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,92 +1071,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>49503000</v>
+      </c>
+      <c r="E17" s="3">
         <v>42618000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>25656000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>21714000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>38958000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>38074000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>34166000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>32214000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>32698000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>36528000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>37030000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>37113000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>35288000</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4214000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2337000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1022000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-6359000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4301000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3229000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3618000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4344000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5166000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2373000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1249000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>39000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1822000</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,218 +1180,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>950000</v>
+      </c>
+      <c r="E20" s="3">
         <v>326000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>42000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1471000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>259000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>24000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-43000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>645000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-327000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-565000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>812000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>34000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-60000</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>7835000</v>
+      </c>
+      <c r="E21" s="3">
         <v>5119000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1505000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-5342000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>6848000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5418000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5671000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6966000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6658000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3487000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3750000</v>
       </c>
-      <c r="N21" s="3" t="s">
+      <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3309000</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1774000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1673000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1577000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>992000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>646000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>605000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>552000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1216000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>620000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>680000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1522000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>797000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>917000</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3390000</v>
+      </c>
+      <c r="E23" s="3">
         <v>990000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2557000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8822000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3914000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2648000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3023000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3773000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4219000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1128000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>539000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-724000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>845000</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>770000</v>
+      </c>
+      <c r="E24" s="3">
         <v>253000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-593000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1753000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>905000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>531000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1069000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1539000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>9000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-4000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-32000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5000</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,93 +1447,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2620000</v>
+      </c>
+      <c r="E26" s="3">
         <v>737000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1964000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-7069000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3009000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2117000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1954000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2234000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4210000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1132000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>571000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-723000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>840000</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2620000</v>
+      </c>
+      <c r="E27" s="3">
         <v>737000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1964000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-7069000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3009000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2117000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1954000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2234000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4210000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1132000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>569000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-723000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>837000</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,9 +1582,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1539,23 +1600,23 @@
       <c r="F29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>5000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>189000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-180000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>3130000</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -1566,9 +1627,12 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1672,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,93 +1717,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-950000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-326000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-42000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1471000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-259000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-24000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>43000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-645000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>327000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>565000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-812000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-34000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>60000</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2620000</v>
+      </c>
+      <c r="E33" s="3">
         <v>737000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1964000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-7069000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3009000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2122000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2143000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2054000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7340000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1132000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>569000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-723000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>837000</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,98 +1852,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2620000</v>
+      </c>
+      <c r="E35" s="3">
         <v>737000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1964000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-7069000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3009000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2122000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2143000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2054000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7340000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1132000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>569000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-723000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>837000</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1969,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,280 +1988,299 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6058000</v>
+      </c>
+      <c r="E41" s="3">
         <v>7166000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>18283000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11269000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2762000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1694000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1482000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2179000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3006000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2002000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3220000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4770000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6246000</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>8330000</v>
+      </c>
+      <c r="E42" s="3">
         <v>9248000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>123000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>414000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2182000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2256000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2316000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2249000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2190000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2382000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1901000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1773000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1516000</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1898000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1801000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1663000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1295000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1364000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1426000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1340000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1176000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1128000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2286000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1414000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1287000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1358000</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1561000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1109000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>983000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>932000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1072000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>985000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>924000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>873000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>738000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>666000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>667000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>695000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>615000</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>640000</v>
+      </c>
+      <c r="E45" s="3">
         <v>734000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>782000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>890000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>814000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>733000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1071000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>832000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>766000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1992000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1500000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1524000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1262000</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18487000</v>
+      </c>
+      <c r="E46" s="3">
         <v>20058000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>21834000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>14800000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8194000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7094000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7133000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7309000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7828000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7547000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8702000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10049000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10997000</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1391000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1373000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1420000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1031000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1851000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1482000</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>8</v>
@@ -2192,96 +2297,105 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>43729000</v>
+      </c>
+      <c r="E48" s="3">
         <v>38337000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>36719000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>36003000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>34928000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>33047000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>26208000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>23318000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21580000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>19467000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>18047000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17292000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>16419000</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7252000</v>
+      </c>
+      <c r="E49" s="3">
         <v>7289000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7330000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7365000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7532000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10841000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8062000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8155000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8659000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8807000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8959000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9120000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9273000</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2435,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,51 +2480,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>245000</v>
+      </c>
+      <c r="E52" s="3">
         <v>301000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>872000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>349000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>106000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>105000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>943000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1358000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2794000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1439000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1104000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1167000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1299000</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,51 +2570,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>71104000</v>
+      </c>
+      <c r="E54" s="3">
         <v>67358000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>68175000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>59548000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>52611000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>49024000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>42346000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>40140000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>40861000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>36595000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>36812000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>37628000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>37988000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2637,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,260 +2656,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3835000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3395000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2562000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1595000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2703000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2363000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2196000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2139000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1869000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1882000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2087000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2312000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1998000</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4190000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3015000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3078000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2093000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1453000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1353000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1693000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>965000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1359000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1423000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1485000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1934000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1311000</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>14180000</v>
+      </c>
+      <c r="E59" s="3">
         <v>13582000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12664000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>9037000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10782000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10123000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8874000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9182000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9186000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9203000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8535000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8572000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8085000</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>22205000</v>
+      </c>
+      <c r="E60" s="3">
         <v>19992000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>18304000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12725000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14938000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13839000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12763000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12286000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12414000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12508000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>12107000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12818000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11394000</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>25148000</v>
+      </c>
+      <c r="E61" s="3">
         <v>28398000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>30580000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>25060000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>13365000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12439000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12699000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10740000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10400000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10524000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10924000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11232000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11424000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>14427000</v>
+      </c>
+      <c r="E62" s="3">
         <v>12072000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>14262000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>15803000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>12777000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>12704000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8150000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8455000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9081000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>11167000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10797000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13097000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>13364000</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2968,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3013,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,51 +3058,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>61780000</v>
+      </c>
+      <c r="E66" s="3">
         <v>60462000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>63146000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>53588000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>41080000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>38982000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>33612000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>31481000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>31895000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>34199000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>33828000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>37147000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>36182000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3125,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3167,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3212,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3089,9 +3257,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,51 +3302,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3831000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1265000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>625000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2626000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9716000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6715000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4549000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3427000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3457000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-3883000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-5015000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-5586000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-4863000</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3392,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3437,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,51 +3482,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9324000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6896000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5029000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5960000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11531000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10042000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8734000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8659000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8966000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2396000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2984000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>481000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1806000</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,98 +3572,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2620000</v>
+      </c>
+      <c r="E81" s="3">
         <v>737000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1964000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-7069000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3009000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2122000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2143000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2054000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7340000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1132000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>569000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-723000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>837000</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,50 +3689,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2671000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2456000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2485000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2488000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2288000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2165000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2096000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1977000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1819000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1679000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1689000</v>
       </c>
-      <c r="N83" s="3" t="s">
+      <c r="O83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1547000</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3776,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3821,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3866,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3911,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,51 +3956,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6911000</v>
+      </c>
+      <c r="E89" s="3">
         <v>6066000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2067000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4133000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6909000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6164000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3474000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5542000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5992000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2634000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1444000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>935000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2408000</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,50 +4023,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7171000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4819000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2107000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1727000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4528000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4070000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3870000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3223000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2747000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2005000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2164000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2016000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-840000</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4110,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,51 +4155,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6106000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13829000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1672000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>50000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4560000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4455000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3803000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3238000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2493000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2256000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2022000</v>
       </c>
-      <c r="N94" s="3" t="s">
+      <c r="O94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1799000</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,8 +4222,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4030,9 +4264,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4309,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4354,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,51 +4399,57 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1892000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3349000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6396000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>12957000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1280000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1501000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-383000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3213000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2495000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1596000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-972000</v>
       </c>
-      <c r="N100" s="3" t="s">
+      <c r="O100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2432000</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4234,55 +4483,61 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1087000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-11112000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>6791000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>8874000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1069000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>208000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-712000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-909000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1004000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1218000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1550000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1476000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1823000</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/UAL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/UAL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
   <si>
     <t>UAL</t>
   </si>
@@ -773,25 +773,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>21060000</v>
+        <v>35716000</v>
       </c>
       <c r="E9" s="3">
-        <v>20393000</v>
+        <v>31769000</v>
       </c>
       <c r="F9" s="3">
-        <v>11862000</v>
+        <v>21369000</v>
       </c>
       <c r="G9" s="3">
-        <v>8375000</v>
+        <v>17826000</v>
       </c>
       <c r="H9" s="3">
-        <v>16427000</v>
+        <v>28477000</v>
       </c>
       <c r="I9" s="3">
-        <v>16605000</v>
+        <v>28109000</v>
       </c>
       <c r="J9" s="3">
-        <v>13968000</v>
+        <v>25013000</v>
       </c>
       <c r="K9" s="3">
         <v>12604000</v>
@@ -818,25 +818,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>32657000</v>
+        <v>18001000</v>
       </c>
       <c r="E10" s="3">
-        <v>24562000</v>
+        <v>13186000</v>
       </c>
       <c r="F10" s="3">
-        <v>12772000</v>
+        <v>3265000</v>
       </c>
       <c r="G10" s="3">
-        <v>6980000</v>
+        <v>-2471000</v>
       </c>
       <c r="H10" s="3">
-        <v>26832000</v>
+        <v>14782000</v>
       </c>
       <c r="I10" s="3">
-        <v>24698000</v>
+        <v>13194000</v>
       </c>
       <c r="J10" s="3">
-        <v>23816000</v>
+        <v>12771000</v>
       </c>
       <c r="K10" s="3">
         <v>23954000</v>
@@ -972,25 +972,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>814000</v>
+        <v>933000</v>
       </c>
       <c r="E14" s="3">
-        <v>140000</v>
+        <v>127000</v>
       </c>
       <c r="F14" s="3">
-        <v>-3367000</v>
+        <v>-3252000</v>
       </c>
       <c r="G14" s="3">
-        <v>-2643000</v>
+        <v>-1038000</v>
       </c>
       <c r="H14" s="3">
-        <v>187000</v>
+        <v>93000</v>
       </c>
       <c r="I14" s="3">
-        <v>482000</v>
+        <v>492000</v>
       </c>
       <c r="J14" s="3">
-        <v>141000</v>
+        <v>176000</v>
       </c>
       <c r="K14" s="3">
         <v>694000</v>
@@ -1078,25 +1078,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>49503000</v>
+        <v>48426000</v>
       </c>
       <c r="E17" s="3">
-        <v>42618000</v>
+        <v>42388000</v>
       </c>
       <c r="F17" s="3">
-        <v>25656000</v>
+        <v>28964000</v>
       </c>
       <c r="G17" s="3">
-        <v>21714000</v>
+        <v>24259000</v>
       </c>
       <c r="H17" s="3">
-        <v>38958000</v>
+        <v>38691000</v>
       </c>
       <c r="I17" s="3">
-        <v>38074000</v>
+        <v>37633000</v>
       </c>
       <c r="J17" s="3">
-        <v>34166000</v>
+        <v>34094000</v>
       </c>
       <c r="K17" s="3">
         <v>32214000</v>
@@ -1123,25 +1123,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4214000</v>
+        <v>5291000</v>
       </c>
       <c r="E18" s="3">
-        <v>2337000</v>
+        <v>2567000</v>
       </c>
       <c r="F18" s="3">
-        <v>-1022000</v>
+        <v>-4330000</v>
       </c>
       <c r="G18" s="3">
-        <v>-6359000</v>
+        <v>-8904000</v>
       </c>
       <c r="H18" s="3">
-        <v>4301000</v>
+        <v>4568000</v>
       </c>
       <c r="I18" s="3">
-        <v>3229000</v>
+        <v>3670000</v>
       </c>
       <c r="J18" s="3">
-        <v>3618000</v>
+        <v>3690000</v>
       </c>
       <c r="K18" s="3">
         <v>4344000</v>
@@ -1187,25 +1187,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>950000</v>
+        <v>24000</v>
       </c>
       <c r="E20" s="3">
-        <v>326000</v>
+        <v>75000</v>
       </c>
       <c r="F20" s="3">
-        <v>42000</v>
+        <v>-62000</v>
       </c>
       <c r="G20" s="3">
-        <v>-1471000</v>
+        <v>14000</v>
       </c>
       <c r="H20" s="3">
-        <v>259000</v>
+        <v>48000</v>
       </c>
       <c r="I20" s="3">
-        <v>24000</v>
+        <v>26000</v>
       </c>
       <c r="J20" s="3">
-        <v>-43000</v>
+        <v>-4000</v>
       </c>
       <c r="K20" s="3">
         <v>645000</v>
@@ -1232,25 +1232,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>7835000</v>
+        <v>7938000</v>
       </c>
       <c r="E21" s="3">
-        <v>5119000</v>
+        <v>4948000</v>
       </c>
       <c r="F21" s="3">
-        <v>1505000</v>
+        <v>-1783000</v>
       </c>
       <c r="G21" s="3">
-        <v>-5342000</v>
+        <v>-6430000</v>
       </c>
       <c r="H21" s="3">
-        <v>6848000</v>
+        <v>6808000</v>
       </c>
       <c r="I21" s="3">
-        <v>5418000</v>
+        <v>5809000</v>
       </c>
       <c r="J21" s="3">
-        <v>5671000</v>
+        <v>5790000</v>
       </c>
       <c r="K21" s="3">
         <v>6966000</v>
@@ -1322,7 +1322,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>3390000</v>
+        <v>3387000</v>
       </c>
       <c r="E23" s="3">
         <v>990000</v>
@@ -1367,7 +1367,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>770000</v>
+        <v>769000</v>
       </c>
       <c r="E24" s="3">
         <v>253000</v>
@@ -1382,10 +1382,10 @@
         <v>905000</v>
       </c>
       <c r="I24" s="3">
-        <v>531000</v>
+        <v>526000</v>
       </c>
       <c r="J24" s="3">
-        <v>1069000</v>
+        <v>880000</v>
       </c>
       <c r="K24" s="3">
         <v>1539000</v>
@@ -1457,7 +1457,7 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2620000</v>
+        <v>2618000</v>
       </c>
       <c r="E26" s="3">
         <v>737000</v>
@@ -1472,10 +1472,10 @@
         <v>3009000</v>
       </c>
       <c r="I26" s="3">
-        <v>2117000</v>
+        <v>2122000</v>
       </c>
       <c r="J26" s="3">
-        <v>1954000</v>
+        <v>2143000</v>
       </c>
       <c r="K26" s="3">
         <v>2234000</v>
@@ -1502,7 +1502,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2620000</v>
+        <v>2618000</v>
       </c>
       <c r="E27" s="3">
         <v>737000</v>
@@ -1517,10 +1517,10 @@
         <v>3009000</v>
       </c>
       <c r="I27" s="3">
-        <v>2117000</v>
+        <v>2122000</v>
       </c>
       <c r="J27" s="3">
-        <v>1954000</v>
+        <v>2143000</v>
       </c>
       <c r="K27" s="3">
         <v>2234000</v>
@@ -1591,26 +1591,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>189000</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3">
         <v>-180000</v>
@@ -1727,25 +1727,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-950000</v>
+        <v>-24000</v>
       </c>
       <c r="E32" s="3">
-        <v>-326000</v>
+        <v>-75000</v>
       </c>
       <c r="F32" s="3">
-        <v>-42000</v>
+        <v>62000</v>
       </c>
       <c r="G32" s="3">
-        <v>1471000</v>
+        <v>-14000</v>
       </c>
       <c r="H32" s="3">
-        <v>-259000</v>
+        <v>-48000</v>
       </c>
       <c r="I32" s="3">
-        <v>-24000</v>
+        <v>-26000</v>
       </c>
       <c r="J32" s="3">
-        <v>43000</v>
+        <v>4000</v>
       </c>
       <c r="K32" s="3">
         <v>-645000</v>
@@ -1772,7 +1772,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2620000</v>
+        <v>2618000</v>
       </c>
       <c r="E33" s="3">
         <v>737000</v>
@@ -1862,7 +1862,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2620000</v>
+        <v>2618000</v>
       </c>
       <c r="E35" s="3">
         <v>737000</v>
@@ -2174,26 +2174,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>640000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>734000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>782000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>890000</v>
-      </c>
-      <c r="H45" s="3">
-        <v>814000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>733000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>1071000</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K45" s="3">
         <v>832000</v>
@@ -2274,16 +2274,16 @@
         <v>1420000</v>
       </c>
       <c r="G47" s="3">
-        <v>1031000</v>
+        <v>1000000</v>
       </c>
       <c r="H47" s="3">
-        <v>1851000</v>
+        <v>1156000</v>
       </c>
       <c r="I47" s="3">
-        <v>1482000</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
+        <v>955000</v>
+      </c>
+      <c r="J47" s="3">
+        <v>806000</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
@@ -2310,25 +2310,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>43729000</v>
+        <v>40179000</v>
       </c>
       <c r="E48" s="3">
-        <v>38337000</v>
+        <v>35517000</v>
       </c>
       <c r="F48" s="3">
-        <v>36719000</v>
+        <v>34504000</v>
       </c>
       <c r="G48" s="3">
-        <v>36003000</v>
+        <v>34837000</v>
       </c>
       <c r="H48" s="3">
-        <v>34928000</v>
+        <v>33568000</v>
       </c>
       <c r="I48" s="3">
-        <v>33047000</v>
+        <v>31484000</v>
       </c>
       <c r="J48" s="3">
-        <v>26208000</v>
+        <v>24864000</v>
       </c>
       <c r="K48" s="3">
         <v>23318000</v>
@@ -2370,7 +2370,7 @@
         <v>7532000</v>
       </c>
       <c r="I49" s="3">
-        <v>10841000</v>
+        <v>7682000</v>
       </c>
       <c r="J49" s="3">
         <v>8062000</v>
@@ -2490,25 +2490,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>245000</v>
+        <v>3795000</v>
       </c>
       <c r="E52" s="3">
-        <v>301000</v>
+        <v>3030000</v>
       </c>
       <c r="F52" s="3">
-        <v>872000</v>
+        <v>2428000</v>
       </c>
       <c r="G52" s="3">
-        <v>349000</v>
+        <v>1384000</v>
       </c>
       <c r="H52" s="3">
-        <v>106000</v>
+        <v>1490000</v>
       </c>
       <c r="I52" s="3">
-        <v>105000</v>
+        <v>1293000</v>
       </c>
       <c r="J52" s="3">
-        <v>943000</v>
+        <v>1435000</v>
       </c>
       <c r="K52" s="3">
         <v>1358000</v>
@@ -2708,22 +2708,22 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4190000</v>
+        <v>4823000</v>
       </c>
       <c r="E58" s="3">
-        <v>3015000</v>
+        <v>3599000</v>
       </c>
       <c r="F58" s="3">
-        <v>3078000</v>
+        <v>4468000</v>
       </c>
       <c r="G58" s="3">
-        <v>2093000</v>
+        <v>2723000</v>
       </c>
       <c r="H58" s="3">
-        <v>1453000</v>
+        <v>2139000</v>
       </c>
       <c r="I58" s="3">
-        <v>1353000</v>
+        <v>2072000</v>
       </c>
       <c r="J58" s="3">
         <v>1693000</v>
@@ -2753,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>14180000</v>
+        <v>10605000</v>
       </c>
       <c r="E59" s="3">
-        <v>13582000</v>
+        <v>11027000</v>
       </c>
       <c r="F59" s="3">
-        <v>12664000</v>
+        <v>9153000</v>
       </c>
       <c r="G59" s="3">
-        <v>9037000</v>
+        <v>6447000</v>
       </c>
       <c r="H59" s="3">
-        <v>10782000</v>
+        <v>7825000</v>
       </c>
       <c r="I59" s="3">
-        <v>10123000</v>
+        <v>7220000</v>
       </c>
       <c r="J59" s="3">
-        <v>8874000</v>
+        <v>6708000</v>
       </c>
       <c r="K59" s="3">
         <v>9182000</v>
@@ -2798,7 +2798,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>22205000</v>
+        <v>22203000</v>
       </c>
       <c r="E60" s="3">
         <v>19992000</v>
@@ -2843,22 +2843,22 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>25148000</v>
+        <v>31916000</v>
       </c>
       <c r="E61" s="3">
-        <v>28398000</v>
+        <v>33701000</v>
       </c>
       <c r="F61" s="3">
-        <v>30580000</v>
+        <v>36595000</v>
       </c>
       <c r="G61" s="3">
-        <v>25060000</v>
+        <v>31186000</v>
       </c>
       <c r="H61" s="3">
-        <v>13365000</v>
+        <v>18311000</v>
       </c>
       <c r="I61" s="3">
-        <v>12439000</v>
+        <v>17715000</v>
       </c>
       <c r="J61" s="3">
         <v>12699000</v>
@@ -2888,25 +2888,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>14427000</v>
+        <v>1414000</v>
       </c>
       <c r="E62" s="3">
-        <v>12072000</v>
+        <v>1369000</v>
       </c>
       <c r="F62" s="3">
-        <v>14262000</v>
+        <v>1284000</v>
       </c>
       <c r="G62" s="3">
-        <v>15803000</v>
+        <v>1156000</v>
       </c>
       <c r="H62" s="3">
-        <v>12777000</v>
+        <v>1024000</v>
       </c>
       <c r="I62" s="3">
-        <v>12704000</v>
+        <v>1010000</v>
       </c>
       <c r="J62" s="3">
-        <v>8150000</v>
+        <v>1832000</v>
       </c>
       <c r="K62" s="3">
         <v>8455000</v>
@@ -3632,7 +3632,7 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2620000</v>
+        <v>2618000</v>
       </c>
       <c r="E81" s="3">
         <v>737000</v>
@@ -3696,25 +3696,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2671000</v>
+        <v>2466000</v>
       </c>
       <c r="E83" s="3">
-        <v>2456000</v>
+        <v>2249000</v>
       </c>
       <c r="F83" s="3">
-        <v>2485000</v>
+        <v>2254000</v>
       </c>
       <c r="G83" s="3">
-        <v>2488000</v>
+        <v>2261000</v>
       </c>
       <c r="H83" s="3">
-        <v>2288000</v>
+        <v>2093000</v>
       </c>
       <c r="I83" s="3">
-        <v>2165000</v>
+        <v>1976000</v>
       </c>
       <c r="J83" s="3">
-        <v>2096000</v>
+        <v>1900000</v>
       </c>
       <c r="K83" s="3">
         <v>1977000</v>
@@ -4453,26 +4453,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/UAL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/UAL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>UAL</t>
   </si>
@@ -656,209 +656,221 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>57063000</v>
+      </c>
+      <c r="E8" s="3">
         <v>53717000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>44955000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>24634000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>15355000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>43259000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>41303000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>37784000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>36558000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>37864000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>38901000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>38279000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>37152000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>37110000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>37534000</v>
+      </c>
+      <c r="E9" s="3">
         <v>35716000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>31769000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>21369000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>17826000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>28477000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>28109000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>25013000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12604000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14420000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18955000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>19611000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>20290000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>20894000</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>19529000</v>
+      </c>
+      <c r="E10" s="3">
         <v>18001000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>13186000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3265000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-2471000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>14782000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>13194000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>12771000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>23954000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>23444000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>19946000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>18668000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>16862000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>16216000</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -876,8 +888,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -920,9 +933,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,99 +981,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>439000</v>
+      </c>
+      <c r="E14" s="3">
         <v>933000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>127000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-3252000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1038000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>93000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>492000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>176000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>694000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>227000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>410000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>470000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1369000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>579000</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2928000</v>
+      </c>
+      <c r="E15" s="3">
         <v>2671000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2456000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2485000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2488000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2288000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2165000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2096000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1977000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1819000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1679000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1689000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1522000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1547000</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,98 +1097,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>51746000</v>
+      </c>
+      <c r="E17" s="3">
         <v>48426000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>42388000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>28964000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>24259000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>38691000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>37633000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>34094000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>32214000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>32698000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>36528000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>37030000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>37113000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>35288000</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5317000</v>
+      </c>
+      <c r="E18" s="3">
         <v>5291000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2567000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4330000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-8904000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4568000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3670000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3690000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4344000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5166000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2373000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1249000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>39000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1822000</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1181,233 +1213,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E20" s="3">
         <v>24000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>75000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-62000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>14000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>48000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>26000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>645000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-327000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-565000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>812000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>34000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-60000</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8211000</v>
+      </c>
+      <c r="E21" s="3">
         <v>7938000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4948000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1783000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-6430000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6808000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5809000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5790000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6966000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6658000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3487000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3750000</v>
       </c>
-      <c r="O21" s="3" t="s">
+      <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3309000</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1402000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1774000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1673000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1577000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>992000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>646000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>605000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>552000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1216000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>620000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>680000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1522000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>797000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>917000</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4168000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3387000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>990000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2557000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8822000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3914000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2648000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3023000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3773000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4219000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1128000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>539000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-724000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>845000</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1019000</v>
+      </c>
+      <c r="E24" s="3">
         <v>769000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>253000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-593000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1753000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>905000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>526000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>880000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1539000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-4000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-32000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5000</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1450,99 +1498,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3149000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2618000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>737000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1964000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-7069000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3009000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2122000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2143000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2234000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4210000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1132000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>571000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-723000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>840000</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3149000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2618000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>737000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1964000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-7069000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3009000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2122000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2143000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2234000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4210000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1132000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>569000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-723000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>837000</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1585,9 +1642,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1613,13 +1673,13 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-180000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>3130000</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>8</v>
@@ -1630,9 +1690,12 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1675,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1720,99 +1786,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-24000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-75000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>62000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-14000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-48000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-26000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-645000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>327000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>565000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-812000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-34000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>60000</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3149000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2618000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>737000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1964000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-7069000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3009000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2122000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2143000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2054000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7340000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1132000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>569000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-723000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>837000</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1855,104 +1930,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3149000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2618000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>737000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1964000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-7069000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3009000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2122000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2143000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2054000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7340000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1132000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>569000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-723000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>837000</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1970,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1989,188 +2074,201 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8769000</v>
+      </c>
+      <c r="E41" s="3">
         <v>6058000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7166000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>18283000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11269000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2762000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1694000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1482000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2179000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3006000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2002000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3220000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4770000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6246000</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5706000</v>
+      </c>
+      <c r="E42" s="3">
         <v>8330000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>9248000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>123000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>414000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2182000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2256000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2316000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2249000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2190000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2382000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1901000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1773000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1516000</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2163000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1898000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1801000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1663000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1295000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1364000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1426000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1340000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1176000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1128000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2286000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1414000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1287000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1358000</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1572000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1561000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1109000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>983000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>932000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1072000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>985000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>924000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>873000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>738000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>666000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>667000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>695000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>615000</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2195,98 +2293,104 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>832000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>766000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1992000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1500000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1524000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1262000</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18883000</v>
+      </c>
+      <c r="E46" s="3">
         <v>18487000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>20058000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>21834000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14800000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8194000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7094000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7133000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7309000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7828000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7547000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8702000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10049000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10997000</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1391000</v>
+        <v>1267000</v>
       </c>
       <c r="E47" s="3">
+        <v>1636000</v>
+      </c>
+      <c r="F47" s="3">
         <v>1373000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1420000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1000000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1156000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>955000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>806000</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>8</v>
@@ -2300,102 +2404,111 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>43296000</v>
+      </c>
+      <c r="E48" s="3">
         <v>40179000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>35517000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>34504000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>34837000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>33568000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>31484000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>24864000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>23318000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21580000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>19467000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>18047000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17292000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>16419000</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7210000</v>
+      </c>
+      <c r="E49" s="3">
         <v>7252000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7289000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7330000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7365000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7532000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7682000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8062000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8155000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8659000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8807000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8959000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9120000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9273000</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2483,54 +2599,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3795000</v>
+        <v>3427000</v>
       </c>
       <c r="E52" s="3">
+        <v>3550000</v>
+      </c>
+      <c r="F52" s="3">
         <v>3030000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2428000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1384000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1490000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1293000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1435000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1358000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2794000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1439000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1104000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1167000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1299000</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,54 +2695,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>74083000</v>
+      </c>
+      <c r="E54" s="3">
         <v>71104000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>67358000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>68175000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>59548000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>52611000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>49024000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>42346000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>40140000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>40861000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>36595000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>36812000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>37628000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>37988000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2638,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2657,278 +2786,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4193000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3835000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3395000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2562000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1595000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2703000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2363000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2196000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2139000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1869000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1882000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2087000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2312000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1998000</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3920000</v>
+      </c>
+      <c r="E58" s="3">
         <v>4823000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3599000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4468000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2723000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2139000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2072000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1693000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>965000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1359000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1423000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1485000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1934000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1311000</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11912000</v>
+      </c>
+      <c r="E59" s="3">
         <v>10605000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11027000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>9153000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6447000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7825000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7220000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6708000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9182000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9186000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9203000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8535000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8572000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8085000</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>23314000</v>
+      </c>
+      <c r="E60" s="3">
         <v>22203000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19992000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>18304000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12725000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>14938000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13839000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12763000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12286000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12414000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>12508000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12107000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12818000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11394000</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>29713000</v>
+      </c>
+      <c r="E61" s="3">
         <v>31916000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>33701000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>36595000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>31186000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>18311000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>17715000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12699000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10740000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10400000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10524000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10924000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11232000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>11424000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1530000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1414000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1369000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1284000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1156000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1024000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1010000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1832000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8455000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9081000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>11167000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>10797000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>13097000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>13364000</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2971,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3016,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3061,54 +3215,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>61408000</v>
+      </c>
+      <c r="E66" s="3">
         <v>61780000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>60462000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>63146000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>53588000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>41080000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>38982000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>33612000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>31481000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>31895000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>34199000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>33828000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>37147000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>36182000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3126,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3170,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3215,9 +3379,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3260,9 +3427,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3305,54 +3475,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6880000</v>
+      </c>
+      <c r="E72" s="3">
         <v>3831000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1265000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>625000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2626000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9716000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6715000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4549000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3427000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3457000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-3883000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-5015000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-5586000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-4863000</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3395,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3440,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3485,54 +3667,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12675000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9324000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6896000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5029000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5960000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11531000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10042000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8734000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8659000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8966000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2396000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2984000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>481000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1806000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3575,104 +3763,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3149000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2618000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>737000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1964000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-7069000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3009000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2122000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2143000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2054000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7340000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1132000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>569000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-723000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>837000</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3690,53 +3887,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2741000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2466000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2249000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2254000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2261000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2093000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1976000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1900000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1977000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1819000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1679000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1689000</v>
       </c>
-      <c r="O83" s="3" t="s">
+      <c r="P83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1547000</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3779,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3824,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3869,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3914,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3959,54 +4172,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9445000</v>
+      </c>
+      <c r="E89" s="3">
         <v>6911000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6066000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2067000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4133000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6909000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6164000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3474000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5542000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5992000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2634000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1444000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>935000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2408000</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4024,53 +4243,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5615000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7171000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4819000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2107000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1727000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4528000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4070000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3870000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3223000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2747000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2005000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2164000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2016000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-840000</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4113,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4158,54 +4384,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2651000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6106000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13829000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1672000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>50000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4560000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4455000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3803000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3238000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2493000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2256000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2022000</v>
       </c>
-      <c r="O94" s="3" t="s">
+      <c r="P94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1799000</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4223,8 +4455,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4267,9 +4500,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4312,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4357,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4402,54 +4644,60 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4182000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1892000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3349000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6396000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>12957000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1280000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1501000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-383000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3213000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2495000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1596000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-972000</v>
       </c>
-      <c r="O100" s="3" t="s">
+      <c r="P100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2432000</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4474,8 +4722,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4486,58 +4734,64 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3" t="s">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2612000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1087000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11112000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6791000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>8874000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1069000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>208000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-712000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-909000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1004000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1218000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1550000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1476000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1823000</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/UAL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/UAL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
   <si>
     <t>UAL</t>
   </si>
@@ -656,221 +656,233 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>59070000</v>
+      </c>
+      <c r="E8" s="3">
         <v>57063000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>53717000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>44955000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>24634000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>15355000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>43259000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>41303000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>37784000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>36558000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>37864000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>38901000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>38279000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>37152000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>37110000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>39008000</v>
+      </c>
+      <c r="E9" s="3">
         <v>37534000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>35716000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>31769000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>21369000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>17826000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>28477000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>28109000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>25013000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12604000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14420000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>18955000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>19611000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>20290000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>20894000</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>20062000</v>
+      </c>
+      <c r="E10" s="3">
         <v>19529000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>18001000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>13186000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3265000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-2471000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>14782000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>13194000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>12771000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>23954000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>23444000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>19946000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>18668000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>16862000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>16216000</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -889,8 +901,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -936,9 +949,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,105 +1000,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>275000</v>
+      </c>
+      <c r="E14" s="3">
         <v>439000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>933000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>127000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-3252000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-1038000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>93000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>492000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>176000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>694000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>227000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>410000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>470000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1369000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>579000</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2939000</v>
+      </c>
+      <c r="E15" s="3">
         <v>2928000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2671000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2456000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2485000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2488000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2288000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2165000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2096000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1977000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1819000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1679000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1689000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1522000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1547000</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1098,104 +1123,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>53975000</v>
+      </c>
+      <c r="E17" s="3">
         <v>51746000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>48426000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>42388000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>28964000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>24259000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>38691000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>37633000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>34094000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>32214000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>32698000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>36528000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>37030000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>37113000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>35288000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5095000</v>
+      </c>
+      <c r="E18" s="3">
         <v>5317000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5291000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2567000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-4330000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-8904000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4568000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3670000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3690000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4344000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5166000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2373000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1249000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>39000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1822000</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1214,248 +1246,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-42000</v>
+      </c>
+      <c r="E20" s="3">
         <v>34000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>24000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>75000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-62000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>14000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>48000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>26000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>645000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-327000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-565000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>812000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>34000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-60000</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8076000</v>
+      </c>
+      <c r="E21" s="3">
         <v>8211000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>7938000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4948000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1783000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-6430000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6808000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5809000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5790000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6966000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6658000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3487000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3750000</v>
       </c>
-      <c r="P21" s="3" t="s">
+      <c r="Q21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3309000</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1167000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1402000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1774000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1673000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1577000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>992000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>646000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>605000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>552000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1216000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>620000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>680000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1522000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>797000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>917000</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4306000</v>
+      </c>
+      <c r="E23" s="3">
         <v>4168000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3387000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>990000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2557000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-8822000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3914000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2648000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3023000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3773000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4219000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1128000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>539000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-724000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>845000</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>953000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1019000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>769000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>253000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-593000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1753000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>905000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>526000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>880000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1539000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-4000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-32000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1501,105 +1549,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3353000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3149000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2618000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>737000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1964000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-7069000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3009000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2122000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2143000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2234000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4210000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1132000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>571000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-723000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>840000</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3353000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3149000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2618000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>737000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1964000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-7069000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3009000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2122000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2143000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2234000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4210000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1132000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>569000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-723000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>837000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1645,9 +1702,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1676,13 +1736,13 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-180000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>3130000</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>8</v>
@@ -1693,9 +1753,12 @@
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1741,9 +1804,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1789,105 +1855,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-34000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-24000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-75000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>62000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-14000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-48000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-26000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-645000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>327000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>565000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-812000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-34000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>60000</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3353000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3149000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2618000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>737000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1964000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-7069000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3009000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2122000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2143000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2054000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7340000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1132000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>569000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-723000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>837000</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1933,110 +2008,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3353000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3149000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2618000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>737000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1964000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-7069000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3009000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2122000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2143000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2054000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7340000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1132000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>569000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-723000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>837000</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2055,8 +2139,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2075,200 +2160,213 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5942000</v>
+      </c>
+      <c r="E41" s="3">
         <v>8769000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6058000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7166000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>18283000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11269000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2762000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1694000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1482000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2179000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3006000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2002000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3220000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4770000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6246000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6298000</v>
+      </c>
+      <c r="E42" s="3">
         <v>5706000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>8330000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>9248000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>123000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>414000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2182000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2256000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2316000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2249000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2190000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2382000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1901000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1773000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1516000</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2391000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2163000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1898000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1801000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1663000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1295000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1364000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1426000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1340000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1176000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1128000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2286000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1414000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1287000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1358000</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1556000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1572000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1561000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1109000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>983000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>932000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1072000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>985000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>924000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>873000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>738000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>666000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>667000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>695000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>615000</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2296,104 +2394,110 @@
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>832000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>766000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1992000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1500000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1524000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1262000</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16857000</v>
+      </c>
+      <c r="E46" s="3">
         <v>18883000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18487000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>20058000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>21834000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>14800000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8194000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7094000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7133000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7309000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7828000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7547000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8702000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10049000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10997000</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1267000</v>
+        <v>1191000</v>
       </c>
       <c r="E47" s="3">
+        <v>1101000</v>
+      </c>
+      <c r="F47" s="3">
         <v>1636000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1373000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1420000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1000000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1156000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>955000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>806000</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>8</v>
@@ -2407,108 +2511,117 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>47573000</v>
+      </c>
+      <c r="E48" s="3">
         <v>43296000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>40179000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>35517000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>34504000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>34837000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>33568000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>31484000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>24864000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>23318000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21580000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>19467000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>18047000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>17292000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>16419000</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7182000</v>
+      </c>
+      <c r="E49" s="3">
         <v>7210000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7252000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7289000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7330000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7365000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7532000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7682000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8062000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8155000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8659000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8807000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8959000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9120000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9273000</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2554,9 +2667,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2602,57 +2718,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3427000</v>
+        <v>3645000</v>
       </c>
       <c r="E52" s="3">
+        <v>3593000</v>
+      </c>
+      <c r="F52" s="3">
         <v>3550000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3030000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2428000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1384000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1490000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1293000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1435000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1358000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2794000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1439000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1104000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1167000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1299000</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2698,57 +2820,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>76448000</v>
+      </c>
+      <c r="E54" s="3">
         <v>74083000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>71104000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>67358000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>68175000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>59548000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>52611000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>49024000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>42346000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>40140000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>40861000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>36595000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>36812000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>37628000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>37988000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2767,8 +2895,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2787,296 +2916,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4567000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4193000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3835000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3395000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2562000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1595000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2703000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2363000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2196000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2139000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1869000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1882000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2087000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2312000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1998000</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5057000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3920000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4823000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3599000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4468000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2723000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2139000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2072000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1693000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>965000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1359000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1423000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1485000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1934000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1311000</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12609000</v>
+      </c>
+      <c r="E59" s="3">
         <v>11912000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10605000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11027000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9153000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6447000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7825000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7220000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6708000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9182000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9186000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9203000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8535000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8572000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8085000</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>26133000</v>
+      </c>
+      <c r="E60" s="3">
         <v>23314000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>22203000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>19992000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>18304000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12725000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>14938000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>13839000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12763000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12286000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>12414000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12508000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12107000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12818000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11394000</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>25979000</v>
+      </c>
+      <c r="E61" s="3">
         <v>29713000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>31916000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>33701000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>36595000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>31186000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>18311000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>17715000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12699000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10740000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10400000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10524000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10924000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>11232000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>11424000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1477000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1530000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1414000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1369000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1284000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1156000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1024000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1010000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1832000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8455000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9081000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>11167000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>10797000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>13097000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>13364000</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3122,9 +3270,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3170,9 +3321,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3218,57 +3372,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>61166000</v>
+      </c>
+      <c r="E66" s="3">
         <v>61408000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>61780000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>60462000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>63146000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>53588000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>41080000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>38982000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>33612000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>31481000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>31895000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>34199000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>33828000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>37147000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>36182000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3287,8 +3447,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3334,9 +3495,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3382,9 +3546,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3430,9 +3597,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3478,57 +3648,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10092000</v>
+      </c>
+      <c r="E72" s="3">
         <v>6880000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3831000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1265000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>625000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2626000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9716000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6715000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4549000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3427000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3457000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-3883000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-5015000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-5586000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-4863000</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3574,9 +3750,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3622,9 +3801,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3670,57 +3852,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15282000</v>
+      </c>
+      <c r="E76" s="3">
         <v>12675000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9324000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6896000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5029000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5960000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11531000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10042000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8734000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8659000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8966000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2396000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2984000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>481000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1806000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3766,110 +3954,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3353000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3149000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2618000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>737000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1964000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-7069000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3009000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2122000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2143000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2054000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7340000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1132000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>569000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-723000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>837000</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3888,56 +4085,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2741000</v>
+        <v>2632000</v>
       </c>
       <c r="E83" s="3">
-        <v>2466000</v>
+        <v>2566000</v>
       </c>
       <c r="F83" s="3">
+        <v>2364000</v>
+      </c>
+      <c r="G83" s="3">
         <v>2249000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2254000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2261000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2093000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1976000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1900000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1977000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1819000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1679000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1689000</v>
       </c>
-      <c r="P83" s="3" t="s">
+      <c r="Q83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1547000</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3983,9 +4184,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4031,9 +4235,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4079,9 +4286,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4127,9 +4337,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4175,57 +4388,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8431000</v>
+      </c>
+      <c r="E89" s="3">
         <v>9445000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6911000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6066000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2067000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4133000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6909000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6164000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3474000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5542000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5992000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2634000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1444000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>935000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2408000</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4244,56 +4463,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5874000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5615000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7171000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4819000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2107000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1727000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4528000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4070000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3870000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3223000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2747000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2005000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2164000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2016000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-840000</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4339,9 +4562,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4387,57 +4613,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6350000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2651000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6106000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13829000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1672000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>50000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4560000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4455000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3803000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3238000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2493000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2256000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2022000</v>
       </c>
-      <c r="P94" s="3" t="s">
+      <c r="Q94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1799000</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4456,8 +4688,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4503,9 +4736,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4551,9 +4787,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4599,9 +4838,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4647,57 +4889,63 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4945000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4182000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1892000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3349000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>6396000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>12957000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1280000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1501000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-383000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3213000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2495000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1596000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-972000</v>
       </c>
-      <c r="P100" s="3" t="s">
+      <c r="Q100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2432000</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4725,8 +4973,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4737,61 +4985,67 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3" t="s">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2864000</v>
+      </c>
+      <c r="E102" s="3">
         <v>2612000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1087000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11112000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6791000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>8874000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1069000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>208000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-712000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-909000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1004000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1218000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1550000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1476000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1823000</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
